--- a/examples/estimate.xlsx
+++ b/examples/estimate.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,16 +32,52 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F1F1F"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -49,11 +85,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -63,6 +113,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -137,6 +197,141 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>cost-core</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. The WBS element's name, e.g. 1.0 Air vehicle. Each name once.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. The number in your estimate for this element, in the units on the Settings sheet.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. The least it could plausibly cost. Leave Low and High blank for an element with no uncertainty.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. The single most likely cost; blank means the point estimate.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. The most it could plausibly cost.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. The shape between Low and High: triangular (the default), pert, uniform, or lognormal (Low and High are then the ends of an 80% range, as a CER gives).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>cost-core</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. What might happen, e.g. Qualification test failure.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. The chance it happens: 0.3 or 30%.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. The least it would cost if it happens.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. The most likely cost if it happens.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. The most it would cost if it happens.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Optional: the element it belongs to, for the report. Must match a name on the Elements sheet.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>cost-core</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. One element of a pair that tends to overrun together.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. The other element of the pair.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. How strongly they move together, -1 to 1 (0.3 is a common default; pairs not listed take the Settings value).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>cost-core</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>What the costs are in: dollars, thousands, millions, billions or any word.</t>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>How much elements not paired on the Correlation sheet move together (0.3 is usual).</t>
+      </text>
+    </comment>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <t>How many simulations: 20,000 is plenty.</t>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="0" shapeId="0">
+      <text>
+        <t>Any whole number; the same seed gives the same answer.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -425,10 +620,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -440,231 +636,438 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Point Estimate</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Most Likely</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Distribution</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>1.0 Program management</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>triangular</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>2.0 Systems engineering</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="7" t="n">
         <v>18.5</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="7" t="n">
         <v>18.5</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>triangular</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>3.0 Antenna subsystem</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>triangular</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>4.0 Software</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>triangular</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>5.0 Facilities</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>pert</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>6.0 Integration and test</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>triangular</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>7.0 Training and support</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="7" t="n">
         <v>6.5</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="7" t="n">
         <v>6.5</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>pert</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>8.0 Initial spares</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Choose one of the listed answers." type="list" errorStyle="stop">
+      <formula1>"triangular,pert,uniform,lognormal"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -676,121 +1079,328 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Most Likely</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Antenna vendor requalification</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="8" t="n">
         <v>0.25</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>3.0 Antenna subsystem</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Cyber accreditation rework</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>4.0 Software</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Site permitting delay</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="8" t="n">
         <v>0.15</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>5.0 Facilities</t>
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="7" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not one of the choices" error="Choose one of the listed answers." type="list" errorStyle="information">
+      <formula1>Elements!$A$2:$A$200</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -799,75 +1409,210 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Element A</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Element B</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Correlation</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>4.0 Software</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>6.0 Integration and test</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="7" t="n">
         <v>0.6</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.0 Program management</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>2.0 Systems engineering</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="7" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>2.0 Systems engineering</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>4.0 Software</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="7" t="n">
         <v>0.4</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="7" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+    </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not one of the choices" error="Choose one of the listed answers." type="list" errorStyle="information">
+      <formula1>Elements!$A$2:$A$200</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not one of the choices" error="Choose one of the listed answers." type="list" errorStyle="information">
+      <formula1>Elements!$A$2:$A$200</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -879,71 +1624,78 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>millions</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Default Correlation</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="7" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Iterations</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="7" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="7" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not one of the choices" error="Choose one of the listed answers." type="list" errorStyle="information">
+      <formula1>"dollars,thousands,millions,billions"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -951,96 +1703,163 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>How to fill in this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Yellow cells</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Yours to fill in. The example rows are there to show the layout: type over them, and add more rows in the yellow space below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Dark blue heading</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>A column that must be filled in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Light blue heading</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>An optional column: leave it blank if it doesn't apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Grey cells</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Labels: leave them as they are.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Hover over a heading</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>A note says what goes in that column, in what units, with an example. A small arrow in a cell means a drop-down list of the allowed answers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Sheet or topic</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>What to put there</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>What this is</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>A cost estimate with its uncertainty. ce-core cost-risk --data &lt;this file&gt; simulates it and says how much it takes to be 50%, 80% or 90% sure, which elements and risks drive that, and what the correlation between elements adds.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Elements sheet</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>One row per WBS element. Element is its name. Point Estimate is the number in the estimate. Low, Most Likely and High are the range you believe: Low the least it could plausibly cost, High the most. Leave Low and High blank for an element with no uncertainty (it is carried at its point estimate).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Distribution</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Optional. triangular (the default) spreads the chance evenly along the three points; pert bunches it toward the most likely; uniform treats every value between Low and High alike and ignores the most likely.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Optional. triangular (the default) spreads the chance evenly along the three points; pert bunches it toward the most likely; uniform treats every value between Low and High alike and ignores the most likely. lognormal takes Low and High as the ends of an 80% range (Lognormal Range on the Settings sheet changes it) and ignores the most likely: the usual shape for an estimate from a CER, and ce-core cer writes the rows to copy here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Risks sheet</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Things that may or may not happen. Probability is the chance it does (0.3 or 30%). Low, Most Likely and High are what it costs if it does. Element is optional and only labels the report. Delete the rows if there are no risks.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Correlation sheet</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Pairs of elements that tend to overrun together, and how strongly (0 none, 1 in lockstep; 0.2 to 0.3 is typical, 0.5 or more for elements driven by the same thing). Every pair not listed takes the Default Correlation on the Settings sheet. Leaving correlation out makes the P80 too low.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Settings sheet</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Units labels the money (thousands, millions or any word). Default Correlation applies to every pair not listed. Iterations and Seed control the simulation; the same seed gives the same answer.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Money</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Use one unit and one dollar basis (for example constant FY2026 $M) throughout.</t>
         </is>
